--- a/AAII_Financials/Yearly/IVTJY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IVTJY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>IVTJY</t>
   </si>
@@ -656,88 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43191</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2578100</v>
+        <v>2808300</v>
       </c>
       <c r="E8" s="3">
+        <v>2630000</v>
+      </c>
+      <c r="F8" s="3">
         <v>2413900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2227900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2473900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2042200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1993100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2369100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3117700</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -765,39 +771,45 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2578100</v>
+        <v>2808300</v>
       </c>
       <c r="E10" s="3">
+        <v>2630000</v>
+      </c>
+      <c r="F10" s="3">
         <v>2413900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2227900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2473900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2042200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1993100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2369100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3117700</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E14" s="3">
         <v>27200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>143300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>104600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-29300</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E15" s="3">
         <v>21400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>38000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>46200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>62300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>65900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>20000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>37200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>49100</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1591600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1487600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1414800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1152500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1625200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1604300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1477100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1662600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2295100</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1090500</v>
+        <v>1216600</v>
       </c>
       <c r="E18" s="3">
+        <v>1142400</v>
+      </c>
+      <c r="F18" s="3">
         <v>999100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1075400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>848600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>437900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>516000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>706500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>822600</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,68 +1047,75 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-51900</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>-40700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-32100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-72100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-24700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-13900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-68200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-42900</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1235200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1163800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1077800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1153700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>983000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>528500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>549900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>811900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>914600</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1104,69 +1143,78 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1190800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1115200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1038800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1105800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>916600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>456800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>386500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>670100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>894800</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E24" s="3">
         <v>219400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>216200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>183500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>185200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>41100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>78400</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>957800</v>
+      </c>
+      <c r="E26" s="3">
         <v>895800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>822600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>922300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>731400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>356500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>345500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>630000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>816400</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>865400</v>
+      </c>
+      <c r="E27" s="3">
         <v>804800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1128300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>946600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>626700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>323000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1358200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>637500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>663300</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1294,29 +1354,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>367700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>74300</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>1152400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>141600</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>51900</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>40700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>32100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>72100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>24700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>13900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>68200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>42900</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>956700</v>
+      </c>
+      <c r="E33" s="3">
         <v>896000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1188500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>995700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>678600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>369700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1413300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>695800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>709600</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>956700</v>
+      </c>
+      <c r="E35" s="3">
         <v>896000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1188500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>995700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>678600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>369700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1413300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>695800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>709600</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43191</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,98 +1643,108 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6781800</v>
+      </c>
+      <c r="E41" s="3">
         <v>8008100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9158700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10224400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11999700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8975800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8833100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9284400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7785300</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9673800</v>
+        <v>10609500</v>
       </c>
       <c r="E42" s="3">
+        <v>9632900</v>
+      </c>
+      <c r="F42" s="3">
         <v>9403000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8676000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8203900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8464600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>8153000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5733200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7842300</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115900</v>
+      </c>
+      <c r="E43" s="3">
         <v>43500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>51500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>96500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>60200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>89900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>281600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1677,159 +1772,177 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1168000</v>
+        <v>2378300</v>
       </c>
       <c r="E45" s="3">
+        <v>1232700</v>
+      </c>
+      <c r="F45" s="3">
         <v>1257500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1675800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2084700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1915600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>73300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>942000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19208600</v>
+        <v>20264300</v>
       </c>
       <c r="E46" s="3">
+        <v>19232400</v>
+      </c>
+      <c r="F46" s="3">
         <v>20200200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21096300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23356300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19863400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17067700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16893100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15627600</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>12322000</v>
+        <v>15294100</v>
       </c>
       <c r="E47" s="3">
+        <v>12329000</v>
+      </c>
+      <c r="F47" s="3">
         <v>10599600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9871000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11310500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10814600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9618600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10287600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10988300</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>416200</v>
+      </c>
+      <c r="E48" s="3">
         <v>288700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>300700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>344600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>440900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>454600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>443900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>340700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>327500</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>136500</v>
+      </c>
+      <c r="E49" s="3">
         <v>105600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>107400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>394900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>410100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>456500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>444400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>617400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>693700</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>785300</v>
+      </c>
+      <c r="E52" s="3">
         <v>880900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>721800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1395700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1438100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1739600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3687400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12720200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16207800</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>75262600</v>
+        <v>84290500</v>
       </c>
       <c r="E54" s="3">
+        <v>75293500</v>
+      </c>
+      <c r="F54" s="3">
         <v>71856200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71620600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>77408500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70880100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>62944600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>75172500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>80698600</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62689700</v>
+      </c>
+      <c r="E57" s="3">
         <v>56740700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>54529500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>53411000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>56914400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>50770300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>44470600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44698300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>47605500</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3337200</v>
+        <v>4235000</v>
       </c>
       <c r="E58" s="3">
+        <v>3220700</v>
+      </c>
+      <c r="F58" s="3">
         <v>2930000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3606900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5669300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5479200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4932900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3739100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3347100</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2117200</v>
+        <v>1903500</v>
       </c>
       <c r="E59" s="3">
+        <v>2123800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1746100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1667900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>417000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>557900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>698200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1130400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1608000</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>62207300</v>
+        <v>68849300</v>
       </c>
       <c r="E60" s="3">
+        <v>62097400</v>
+      </c>
+      <c r="F60" s="3">
         <v>59218300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>58685900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>63000700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>56807400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>50101700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>49567800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>52560600</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3415000</v>
+        <v>3876000</v>
       </c>
       <c r="E61" s="3">
+        <v>3504000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3570200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3743200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4176900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4484100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4501000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5778100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6097900</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2327600</v>
+        <v>3514700</v>
       </c>
       <c r="E62" s="3">
+        <v>2379300</v>
+      </c>
+      <c r="F62" s="3">
         <v>2143500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2583500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2635000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2184200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2171100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12957700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14748700</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>67956800</v>
+        <v>76274300</v>
       </c>
       <c r="E66" s="3">
+        <v>67987600</v>
+      </c>
+      <c r="F66" s="3">
         <v>64942300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>65053200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>69863600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>63561400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>56847000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>68334300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73452400</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,39 +2543,45 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E70" s="3">
         <v>165500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>160600</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>168600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>229900</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>239800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>209800</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>252800</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>306900</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7261700</v>
+      </c>
+      <c r="E72" s="3">
         <v>6642800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6081000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5565200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5402000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5255400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4525300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3459700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3318200</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7850600</v>
+      </c>
+      <c r="E76" s="3">
         <v>7142000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6752900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5841100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6610000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6296000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5176600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5763800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5982000</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43191</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>956700</v>
+      </c>
+      <c r="E81" s="3">
         <v>896000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1188500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>995700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>678600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>369700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1413300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>695800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>709600</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E83" s="3">
         <v>37600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>43100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>55400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>57800</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>16600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26300</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3753400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1486900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2218600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2746700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2792900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-283700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>732700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1760900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2104300</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-37500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-48400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-124800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-34500</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45400</v>
+      </c>
+      <c r="E94" s="3">
         <v>14300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-264400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>46800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-436800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-85200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-53100</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>414500</v>
+        <v>536800</v>
       </c>
       <c r="E96" s="3">
+        <v>510600</v>
+      </c>
+      <c r="F96" s="3">
         <v>374700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>322500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>234500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>73500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>332100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>447400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>333000</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2344000</v>
+      </c>
+      <c r="E100" s="3">
         <v>30800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1914700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2137600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6057700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-755500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-767800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3306800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2806900</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-120600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-135000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>119500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>201200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-565100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-178300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-75900</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1388700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1441100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-688900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-761300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3431000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-836100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1037100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1282400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>573600</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
